--- a/docs/reports/GFI.xlsx
+++ b/docs/reports/GFI.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Basic Materials · Cyclical / Commodities (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
+          <t>Basic Materials · Cyclical / Commodities (mid-cycle multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>42.69814807661425</v>
+        <v>58.37797951135433</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +699,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -744,10 +741,10 @@
           <t>Treasury Shares Number</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>0.605707</v>
       </c>
     </row>
@@ -757,16 +754,16 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>891.378571</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>893.540813</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>895.0242469999999</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>894.41854</v>
       </c>
     </row>
@@ -776,16 +773,16 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>891.378571</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>893.540813</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>895.0242469999999</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>895.0242469999999</v>
       </c>
     </row>
@@ -795,16 +792,16 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>309.9</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>587.8</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>1635.4</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>959</v>
       </c>
     </row>
@@ -814,16 +811,16 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>1473.5</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>1672.9</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>2945.8</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>3221.2</v>
       </c>
     </row>
@@ -833,16 +830,16 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>4207.6</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>4476.1</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>5201.4</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>8432.6</v>
       </c>
     </row>
@@ -852,16 +849,16 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>5286.9</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>5712.6</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>7697</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>11170.8</v>
       </c>
     </row>
@@ -871,16 +868,16 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>1017</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>381.9</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>237.4</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>1348.5</v>
       </c>
     </row>
@@ -890,16 +887,16 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>4207.6</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>4476.1</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>5201.4</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>8432.6</v>
       </c>
     </row>
@@ -909,16 +906,16 @@
           <t>Capital Lease Obligations</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>394.2</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>436.4</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>450.2</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>483</v>
       </c>
     </row>
@@ -928,16 +925,16 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>4207.6</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>4476.1</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>5201.4</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>8432.6</v>
       </c>
     </row>
@@ -947,16 +944,16 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>5286.9</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>5129.5</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>6977.9</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>10992.1</v>
       </c>
     </row>
@@ -966,16 +963,16 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>4339.5</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>4619.8</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>5366.9</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>8672.4</v>
       </c>
     </row>
@@ -985,16 +982,16 @@
           <t>Minority Interest</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>131.9</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>143.7</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>165.5</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>239.8</v>
       </c>
     </row>
@@ -1004,16 +1001,16 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>4207.6</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>4476.1</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>5201.4</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>8432.6</v>
       </c>
     </row>
@@ -1023,16 +1020,16 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-2293.1</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-2359.3</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-2528.1</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-2089.5</v>
       </c>
     </row>
@@ -1042,16 +1039,16 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-2293.1</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-2359.3</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>-2528.1</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-2089.5</v>
       </c>
     </row>
@@ -1061,16 +1058,16 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>2629.2</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>2963.9</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>3858</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>6677.3</v>
       </c>
     </row>
@@ -1080,16 +1077,16 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>3844.8</v>
       </c>
     </row>
@@ -1099,16 +1096,16 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>3871.5</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>3844.8</v>
       </c>
     </row>
@@ -1118,16 +1115,16 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>2998.6</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>3606.5</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>4776</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>6552.8</v>
       </c>
     </row>
@@ -1137,16 +1134,16 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>2213.2</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>2100.7</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>3065.6</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>4852.9</v>
       </c>
     </row>
@@ -1156,7 +1153,7 @@
           <t>Derivative Product Liabilities</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1166,16 +1163,16 @@
           <t>Employee Benefits</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>22.4</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>40.5</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>20.4</v>
       </c>
     </row>
@@ -1185,16 +1182,16 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>399.8</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>389.3</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>503.8</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>1401.7</v>
       </c>
     </row>
@@ -1204,16 +1201,16 @@
           <t>Non Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>399.8</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>389.3</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>503.8</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>1401.7</v>
       </c>
     </row>
@@ -1223,16 +1220,16 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>1409.4</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>1013.1</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>2139.8</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>2938.6</v>
       </c>
     </row>
@@ -1242,16 +1239,16 @@
           <t>Long Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>330.1</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>359.7</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>363.3</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>379.1</v>
       </c>
     </row>
@@ -1261,16 +1258,16 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>1079.3</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>653.4</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>1776.5</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>2559.5</v>
       </c>
     </row>
@@ -1280,16 +1277,16 @@
           <t>Long Term Provisions</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>381.6</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>657.8</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>402</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>492.2</v>
       </c>
     </row>
@@ -1299,16 +1296,16 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>785.4</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>1505.8</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>1710.4</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>1699.9</v>
       </c>
     </row>
@@ -1318,13 +1315,13 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>10.2</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>1373.2</v>
       </c>
     </row>
@@ -1334,16 +1331,16 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>659.8</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>806</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>282.6</v>
       </c>
     </row>
@@ -1353,16 +1350,16 @@
           <t>Current Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>76.7</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>103.9</v>
       </c>
     </row>
@@ -1372,13 +1369,13 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>583.1</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>719.1</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>178.7</v>
       </c>
     </row>
@@ -1388,13 +1385,13 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>583.1</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>719.1</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>178.7</v>
       </c>
     </row>
@@ -1404,10 +1401,10 @@
           <t>Line Of Credit</t>
         </is>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>719.1</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>178.7</v>
       </c>
     </row>
@@ -1417,16 +1414,16 @@
           <t>Pensionand Other Post Retirement Benefit Plans Current</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>30.6</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>38.4</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>44.1</v>
       </c>
     </row>
@@ -1436,16 +1433,16 @@
           <t>Current Provisions</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>18.5</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>79.2</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>108.3</v>
       </c>
     </row>
@@ -1455,16 +1452,16 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>662</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>760.6</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>794.2</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>1264.9</v>
       </c>
     </row>
@@ -1474,16 +1471,16 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>412</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>428</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>454.6</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>595.8</v>
       </c>
     </row>
@@ -1493,16 +1490,16 @@
           <t>Interest Payable</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>7.3</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>7.8</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>6.4</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>10.3</v>
       </c>
     </row>
@@ -1512,16 +1509,16 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>250</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>332.6</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>339.6</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>669.1</v>
       </c>
     </row>
@@ -1531,16 +1528,16 @@
           <t>Other Payable</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>63.3</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>75.5</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>132.6</v>
       </c>
     </row>
@@ -1550,16 +1547,16 @@
           <t>Total Tax Payable</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>53.6</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>95.7</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>112.4</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>311.5</v>
       </c>
     </row>
@@ -1569,16 +1566,16 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>133.1</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>161.8</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>151.7</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1588,16 +1585,16 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>7338.1</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>8226.299999999999</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>10142.9</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>15225.2</v>
       </c>
     </row>
@@ -1607,16 +1604,16 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>5535.7</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>6338.6</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>8195.1</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>12176.8</v>
       </c>
     </row>
@@ -1626,16 +1623,16 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>205.3</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>252</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>394.4</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>395.4</v>
       </c>
     </row>
@@ -1645,16 +1642,16 @@
           <t>Non Current Deferred Assets</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>195.5</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>172.2</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>154.9</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>38.2</v>
       </c>
     </row>
@@ -1664,16 +1661,16 @@
           <t>Non Current Deferred Taxes Assets</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>195.5</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>172.2</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>154.9</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>38.2</v>
       </c>
     </row>
@@ -1683,13 +1680,13 @@
           <t>Non Current Note Receivables</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="25" t="n">
         <v>27.3</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>23.4</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1699,13 +1696,13 @@
           <t>Non Current Accounts Receivable</t>
         </is>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>75.7</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>69.7</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>73.09999999999999</v>
       </c>
     </row>
@@ -1715,7 +1712,7 @@
           <t>Financial Assets</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1725,16 +1722,16 @@
           <t>Investments And Advances</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>295.8</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>764.3</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>277.7</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>333.3</v>
       </c>
     </row>
@@ -1744,16 +1741,16 @@
           <t>Other Investments</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>176.4</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>109.6</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>113.4</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>148.1</v>
       </c>
     </row>
@@ -1763,16 +1760,16 @@
           <t>Investmentin Financial Assets</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>34.5</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>106.1</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>151.7</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="25" t="n">
         <v>182.4</v>
       </c>
     </row>
@@ -1782,13 +1779,13 @@
           <t>Held To Maturity Securities</t>
         </is>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="25" t="n">
         <v>40.4</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="25" t="n">
         <v>37.2</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="25" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1798,16 +1795,16 @@
           <t>Available For Sale Securities</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="25" t="n">
         <v>34.5</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="25" t="n">
         <v>65.7</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="25" t="n">
         <v>114.5</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="25" t="n">
         <v>142.4</v>
       </c>
     </row>
@@ -1817,16 +1814,16 @@
           <t>Long Term Equity Investment</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="25" t="n">
         <v>548.6</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="25" t="n">
         <v>12.6</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="25" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -1836,16 +1833,16 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="25" t="n">
         <v>4815.7</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="25" t="n">
         <v>5074.4</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="25" t="n">
         <v>7298.4</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="25" t="n">
         <v>11336.8</v>
       </c>
     </row>
@@ -1855,16 +1852,16 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>-7977.1</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="25" t="n">
         <v>-8695.5</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="25" t="n">
         <v>-8980.799999999999</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="25" t="n">
         <v>-9535.700000000001</v>
       </c>
     </row>
@@ -1874,16 +1871,16 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>12792.8</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="25" t="n">
         <v>13769.9</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="25" t="n">
         <v>16279.2</v>
       </c>
-      <c r="F67" s="29" t="n">
+      <c r="F67" s="25" t="n">
         <v>20872.5</v>
       </c>
     </row>
@@ -1893,16 +1890,16 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>1802.4</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="25" t="n">
         <v>1887.7</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="25" t="n">
         <v>1947.8</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F68" s="25" t="n">
         <v>3048.4</v>
       </c>
     </row>
@@ -1912,10 +1909,10 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="25" t="n">
         <v>23.3</v>
       </c>
-      <c r="F69" s="29" t="n">
+      <c r="F69" s="25" t="n">
         <v>28.1</v>
       </c>
     </row>
@@ -1925,10 +1922,10 @@
           <t>Hedging Assets Current</t>
         </is>
       </c>
-      <c r="B70" s="29" t="n">
+      <c r="B70" s="25" t="n">
         <v>5.1</v>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1938,16 +1935,16 @@
           <t>Assets Held For Sale Current</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="25" t="n">
         <v>153.3</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="25" t="n">
         <v>21.1</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="25" t="n">
         <v>77.5</v>
       </c>
     </row>
@@ -1957,10 +1954,10 @@
           <t>Current Deferred Assets</t>
         </is>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="25" t="n">
         <v>23.3</v>
       </c>
     </row>
@@ -1970,16 +1967,16 @@
           <t>Prepaid Assets</t>
         </is>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="25" t="n">
         <v>66.3</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="25" t="n">
         <v>59.3</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="25" t="n">
         <v>50.8</v>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F73" s="25" t="n">
         <v>81.59999999999999</v>
       </c>
     </row>
@@ -1989,16 +1986,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="25" t="n">
         <v>759</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="25" t="n">
         <v>827.9</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="25" t="n">
         <v>699.3</v>
       </c>
-      <c r="F74" s="29" t="n">
+      <c r="F74" s="25" t="n">
         <v>782.6</v>
       </c>
     </row>
@@ -2008,16 +2005,16 @@
           <t>Work In Process</t>
         </is>
       </c>
-      <c r="C75" s="29" t="n">
+      <c r="C75" s="25" t="n">
         <v>520.4</v>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="25" t="n">
         <v>562.7</v>
       </c>
-      <c r="E75" s="29" t="n">
+      <c r="E75" s="25" t="n">
         <v>441.2</v>
       </c>
-      <c r="F75" s="29" t="n">
+      <c r="F75" s="25" t="n">
         <v>471.8</v>
       </c>
     </row>
@@ -2027,16 +2024,16 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="25" t="n">
         <v>238.6</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="25" t="n">
         <v>265.2</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="25" t="n">
         <v>258.1</v>
       </c>
-      <c r="F76" s="29" t="n">
+      <c r="F76" s="25" t="n">
         <v>310.8</v>
       </c>
     </row>
@@ -2046,16 +2043,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="25" t="n">
         <v>207.7</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="25" t="n">
         <v>198.5</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="25" t="n">
         <v>293.1</v>
       </c>
-      <c r="F77" s="29" t="n">
+      <c r="F77" s="25" t="n">
         <v>299.4</v>
       </c>
     </row>
@@ -2065,16 +2062,16 @@
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="C78" s="29" t="n">
+      <c r="C78" s="25" t="n">
         <v>22.5</v>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E78" s="25" t="n">
         <v>27.4</v>
       </c>
-      <c r="F78" s="29" t="n">
+      <c r="F78" s="25" t="n">
         <v>31.8</v>
       </c>
     </row>
@@ -2084,16 +2081,16 @@
           <t>Taxes Receivable</t>
         </is>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C79" s="25" t="n">
         <v>129.4</v>
       </c>
-      <c r="D79" s="29" t="n">
+      <c r="D79" s="25" t="n">
         <v>98.8</v>
       </c>
-      <c r="E79" s="29" t="n">
+      <c r="E79" s="25" t="n">
         <v>113</v>
       </c>
-      <c r="F79" s="29" t="n">
+      <c r="F79" s="25" t="n">
         <v>123.5</v>
       </c>
     </row>
@@ -2103,16 +2100,16 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C80" s="29" t="n">
+      <c r="C80" s="25" t="n">
         <v>55.8</v>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="25" t="n">
         <v>68.7</v>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="25" t="n">
         <v>152.7</v>
       </c>
-      <c r="F80" s="29" t="n">
+      <c r="F80" s="25" t="n">
         <v>144.1</v>
       </c>
     </row>
@@ -2122,16 +2119,16 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="C81" s="29" t="n">
+      <c r="C81" s="25" t="n">
         <v>769.4</v>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="25" t="n">
         <v>648.7</v>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E81" s="25" t="n">
         <v>860.2</v>
       </c>
-      <c r="F81" s="29" t="n">
+      <c r="F81" s="25" t="n">
         <v>1779.2</v>
       </c>
     </row>
@@ -2141,16 +2138,16 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="C82" s="29" t="n">
+      <c r="C82" s="25" t="n">
         <v>769.4</v>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="25" t="n">
         <v>648.7</v>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="25" t="n">
         <v>860.2</v>
       </c>
-      <c r="F82" s="29" t="n">
+      <c r="F82" s="25" t="n">
         <v>1779.2</v>
       </c>
     </row>
@@ -2160,16 +2157,16 @@
           <t>Cash Financial</t>
         </is>
       </c>
-      <c r="C83" s="29" t="n">
+      <c r="C83" s="25" t="n">
         <v>769.4</v>
       </c>
-      <c r="D83" s="29" t="n">
+      <c r="D83" s="25" t="n">
         <v>648.7</v>
       </c>
-      <c r="E83" s="29" t="n">
+      <c r="E83" s="25" t="n">
         <v>860.2</v>
       </c>
-      <c r="F83" s="29" t="n">
+      <c r="F83" s="25" t="n">
         <v>1779.2</v>
       </c>
     </row>
@@ -2205,7 +2202,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -2247,16 +2244,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>309.9</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>138.1</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>423.6</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>2373.7</v>
       </c>
     </row>
@@ -2266,13 +2263,13 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>-36.3</v>
       </c>
     </row>
@@ -2282,16 +2279,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-263.4</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-722.4</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-1078.5</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>-4222.8</v>
       </c>
     </row>
@@ -2301,16 +2298,16 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>206.5</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>804.8</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>2291.1</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>4085.8</v>
       </c>
     </row>
@@ -2320,10 +2317,10 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2333,16 +2330,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>-1069.3</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>-1054.7</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>-1183.4</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>-1398.5</v>
       </c>
     </row>
@@ -2352,16 +2349,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>769.4</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>648.7</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>860.2</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>1779.2</v>
       </c>
     </row>
@@ -2371,16 +2368,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>524.7</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>769.4</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>648.7</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>860.2</v>
       </c>
     </row>
@@ -2390,16 +2387,16 @@
           <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>-5.4</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>-26.2</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>-17.5</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>85.90000000000001</v>
       </c>
     </row>
@@ -2409,16 +2406,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>250.1</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-94.5</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>229</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>833.1</v>
       </c>
     </row>
@@ -2428,16 +2425,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-56.9</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>1212.6</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>-173.3</v>
       </c>
     </row>
@@ -2447,16 +2444,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>-56.9</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>1212.6</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>-173.3</v>
       </c>
     </row>
@@ -2466,16 +2463,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-36.3</v>
       </c>
     </row>
@@ -2485,13 +2482,13 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>-36.3</v>
       </c>
     </row>
@@ -2501,10 +2498,10 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2514,16 +2511,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-56.9</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>1212.6</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-137</v>
       </c>
     </row>
@@ -2533,16 +2530,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-56.9</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>1212.6</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-137</v>
       </c>
     </row>
@@ -2552,16 +2549,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>-263.4</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>-722.4</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>-1078.5</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>-4222.8</v>
       </c>
     </row>
@@ -2571,16 +2568,16 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>206.5</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>804.8</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>2291.1</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>4085.8</v>
       </c>
     </row>
@@ -2590,16 +2587,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>-1072.2</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>-1369.7</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>-2590.6</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>-2765.8</v>
       </c>
     </row>
@@ -2609,16 +2606,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>-1072.2</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>-1369.7</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>-2590.6</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>-2765.8</v>
       </c>
     </row>
@@ -2628,16 +2625,16 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>26.3</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>35.5</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-23.8</v>
       </c>
     </row>
@@ -2647,16 +2644,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>-31.2</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-36.3</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>-14.2</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>778.5</v>
       </c>
     </row>
@@ -2666,16 +2663,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>56.6</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>882</v>
       </c>
     </row>
@@ -2685,16 +2682,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>-32.7</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-41.3</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>-70.8</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-103.5</v>
       </c>
     </row>
@@ -2704,16 +2701,16 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>-316.2</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>-1390.5</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>-2124.2</v>
       </c>
     </row>
@@ -2723,16 +2720,16 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>127.3</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2742,16 +2739,16 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-316.2</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-1517.8</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-2124.2</v>
       </c>
     </row>
@@ -2761,16 +2758,16 @@
           <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-1067.3</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>-1052.7</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>-1180.7</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>-1396.3</v>
       </c>
     </row>
@@ -2780,16 +2777,16 @@
           <t>Sale Of PPE</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>2.7</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -2799,16 +2796,16 @@
           <t>Purchase Of PPE</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-1069.3</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-1054.7</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-1183.4</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-1398.5</v>
       </c>
     </row>
@@ -2818,10 +2815,10 @@
           <t>Capital Expenditure Reported</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>28.7</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>26.3</v>
       </c>
     </row>
@@ -2831,16 +2828,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>1379.2</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>1192.8</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>1607</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>3772.2</v>
       </c>
     </row>
@@ -2850,16 +2847,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>1379.2</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>1192.8</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>1607</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>3772.2</v>
       </c>
     </row>
@@ -2869,16 +2866,16 @@
           <t>Taxes Refund Paid</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-611.7</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>-421.8</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>-525.5</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>-789.7</v>
       </c>
     </row>
@@ -2888,16 +2885,16 @@
           <t>Interest Received Cfo</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>12.1</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>23.4</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>17.4</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>41.2</v>
       </c>
     </row>
@@ -2907,16 +2904,16 @@
           <t>Interest Paid Cfo</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>-97.2</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>-104.8</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>-130.4</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>-159.9</v>
       </c>
     </row>
@@ -2926,16 +2923,16 @@
           <t>Dividend Paid Cfo</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>-335.6</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>-382.8</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>-379.2</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>-761.9</v>
       </c>
     </row>
@@ -2945,16 +2942,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-134.2</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>-199.1</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>13.9</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>187.4</v>
       </c>
     </row>
@@ -2964,16 +2961,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>22.4</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>15.4</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>206.4</v>
       </c>
     </row>
@@ -2983,16 +2980,16 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>22.4</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>15.4</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>206.4</v>
       </c>
     </row>
@@ -3002,16 +2999,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>-195.1</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>-153.1</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>42.6</v>
       </c>
     </row>
@@ -3021,16 +3018,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>38.5</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>-61.4</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>-96.8</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>-61.6</v>
       </c>
     </row>
@@ -3040,16 +3037,16 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>20.1</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>52.1</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>-10.2</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>117.9</v>
       </c>
     </row>
@@ -3059,16 +3056,16 @@
           <t>Stock Based Compensation</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>6.9</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>9.1</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>4.4</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>25.4</v>
       </c>
     </row>
@@ -3078,10 +3075,10 @@
           <t>Provisionand Write Offof Assets</t>
         </is>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>66.7</v>
       </c>
     </row>
@@ -3091,16 +3088,16 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>505</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>156.4</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>-281.3</v>
       </c>
     </row>
@@ -3110,16 +3107,16 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>442.1</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>465.1</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>697.1</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>1649.2</v>
       </c>
     </row>
@@ -3129,16 +3126,16 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>442.1</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>465.1</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>697.1</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>1649.2</v>
       </c>
     </row>
@@ -3148,16 +3145,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>844.3</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>795.3</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>627.4</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>920.4</v>
       </c>
     </row>
@@ -3167,16 +3164,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>844.3</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>795.3</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>627.4</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>920.4</v>
       </c>
     </row>
@@ -3186,16 +3183,16 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>18.7</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>54.7</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>-821.9</v>
       </c>
     </row>
@@ -3205,16 +3202,16 @@
           <t>Pension And Employee Benefit Expense</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>55.8</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>14.5</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>43.2</v>
       </c>
     </row>
@@ -3224,16 +3221,16 @@
           <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>31.3</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>52.1</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -3243,13 +3240,13 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="25" t="n">
         <v>57</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>-58.1</v>
       </c>
     </row>
@@ -3259,16 +3256,16 @@
           <t>Gain Loss On Sale Of Business</t>
         </is>
       </c>
-      <c r="B60" s="29" t="n">
+      <c r="B60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>-808.2</v>
       </c>
     </row>
@@ -3278,16 +3275,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>708.7</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>745.2</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>1290.5</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="25" t="n">
         <v>3645.4</v>
       </c>
     </row>
@@ -3297,6 +3294,314 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GFI — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>87.03737370184209</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>79.37844742798252</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>95.62429432191867</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>53.51526170385419</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>43.88251459716043</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>63.14800881054794</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>50.05950935426196</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40.7103386756712</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>59.40868003285271</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mid-cycle normalized EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>26.56104004462651</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>20.71761123480868</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>32.40446885444434</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>SUMPRODUCT(C5:C8,F5:F8)/SUM(F5:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>0.08200884281181614</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>$B$11*(1+$B$12)-$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>54.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B17" s="17">
+        <f>(1-$B$16)*$B$14+$B$16*$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>32.88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>58.37797951135433</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 15% to the Street consensus ($54.28); model-only target $59.10.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3321,14 +3626,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GFI — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>GFI — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -3390,40 +3695,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>9013.839</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>9284.25417</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>9562.7817951</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>9849.665248953001</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>10145.15520642159</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>10449.50986261424</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>10762.99515849267</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>11085.88501324745</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>11418.46156364487</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>11761.01541055422</v>
+      <c r="B5" s="18" t="n">
+        <v>10939.125</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>11643.91000521689</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>12264.11978195723</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>12819.22049619522</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>13325.904900273</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>13797.81273554226</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>14245.75387532036</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>14678.12947531077</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>15101.38970019858</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>15478.92444270354</v>
       </c>
     </row>
     <row r="6">
@@ -3437,39 +3742,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3480,35 +3785,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>0.5034109218059031</v>
+      <c r="B7" s="11" t="n">
+        <v>0.716713632439664</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.688857035586033</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.6610004387324019</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.6331438418787708</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.6052872450251399</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.5774306481715088</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.5495740513178777</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.5217174544642467</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.5217174544642467</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.5217174544642467</v>
       </c>
     </row>
     <row r="8">
@@ -3517,43 +3822,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3564,35 +3869,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>5021.972274206601</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>3784.65466</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>3898.194299799999</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>4015.140128794</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>4135.59433265782</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>4259.662162637555</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>4387.452027516681</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>4519.075588342183</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>4654.647855992447</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>4794.28729167222</v>
+      <c r="B9" s="18" t="n">
+        <v>5017.688009400001</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>5135.188063735764</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>5190.827561751298</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>5197.211834653883</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>5164.445171959616</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>5100.276968301623</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>5010.457836369158</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>4899.138625001247</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>5042.673085619126</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>5170.701287759604</v>
       </c>
     </row>
     <row r="10">
@@ -3643,40 +3948,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>2188.901839348277</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>2265.513403725467</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>2344.806372855858</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>2426.874595905813</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>2511.815206762516</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>2599.728738999204</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>2690.719244864176</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>2784.894418434422</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>2882.365723079627</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>2983.248523387413</v>
+      <c r="B12" s="20" t="n">
+        <v>4354.242269607347</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>4438.499337886294</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>4524.715468845498</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>4572.950611125078</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>4591.318735028943</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>4586.078981079316</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>4561.91298090575</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>4522.236594737328</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>4742.923531640906</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>4952.438079472667</v>
       </c>
     </row>
     <row r="13">
@@ -3685,43 +3990,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3729,438 +4034,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GFI — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>1.093</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>894.41854</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>2188.901839348277</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="12">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>2265.513403725467</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>2344.806372855858</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>2426.874595905813</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="12">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>2511.815206762516</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="12">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>2599.728738999204</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="12">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>2690.719244864176</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>2784.894418434422</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>2882.365723079627</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="12">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>2983.248523387413</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="12">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="12">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="12">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>32.88</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="13">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +4049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4200,7 +4075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-08, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4102,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="18" t="n">
         <v>894.41854</v>
       </c>
     </row>
@@ -4237,7 +4112,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="18" t="n">
         <v>3221.2</v>
       </c>
     </row>
@@ -4247,7 +4122,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="18" t="n">
         <v>1779.2</v>
       </c>
     </row>
@@ -4257,7 +4132,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="18" t="n">
         <v>239.8</v>
       </c>
     </row>
@@ -4267,7 +4142,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4285,7 +4160,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -4295,7 +4170,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -4305,7 +4180,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4315,7 +4190,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4325,8 +4200,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>0.52</v>
+      <c r="B17" s="22" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="18">
@@ -4335,7 +4210,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.04899999999999999</v>
       </c>
     </row>
@@ -4345,7 +4220,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -4362,7 +4237,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4404,6 +4279,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4411,20 +4311,35 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>0.19375</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.1375</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0.08124999999999999</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0.02499999999999999</v>
+      <c r="C26" s="11" t="n">
+        <v>0.06442791404402876</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.05326473465206037</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.04526217324252213</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.03952536772638876</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.03541281727589028</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.032464648445636</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.03035119122333507</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.02883611468339666</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -4433,20 +4348,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0.5034109218059031</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0.4922418298733763</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>0.4810727379408495</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>0.4699036460083227</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0.4587345540757959</v>
+      <c r="B27" s="11" t="n">
+        <v>0.716713632439664</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.688857035586033</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.6610004387324019</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.6331438418787708</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.6052872450251399</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.5774306481715088</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.5495740513178777</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.5217174544642467</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.5217174544642467</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.5217174544642467</v>
       </c>
     </row>
     <row r="28">
@@ -4455,19 +4385,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.1498633894474192</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.1498633894474192</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.1498633894474192</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.1498633894474192</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.1498633894474192</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.1498633894474192</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.1498633894474192</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.1498633894474192</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.1498633894474192</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.1498633894474192</v>
       </c>
     </row>
@@ -4477,20 +4422,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.2177747588473552</v>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>0.2177747588473552</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>0.2177747588473552</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>0.2177747588473552</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>0.2177747588473552</v>
+      <c r="C29" s="11" t="n">
+        <v>0.2118941999078892</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.2060136409684232</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.2001330820289572</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.1942525230894911</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.1883719641500252</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.1824914052105591</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.1766108462710931</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.1707302873316272</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.1648497283921611</v>
       </c>
     </row>
     <row r="30">
@@ -4499,7 +4459,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="11" t="n">
         <v>-0.03631241940942298</v>
       </c>
     </row>
@@ -4563,7 +4523,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -4574,7 +4534,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -4585,7 +4545,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4596,18 +4556,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -4623,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4636,6 +4596,11 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4703,6 +4668,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4710,36 +4700,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>4286.7</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>4500.7</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>5201.6</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>8751.299999999999</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="19">
         <f>I5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>J5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19">
+        <f>K5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
+        <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="19">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4749,36 +4759,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -4788,36 +4818,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>1436.4</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>1467.1</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>2093.2</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>4405.5</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="19">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="19">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="19">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="19">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="19">
         <f>J5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>K5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>L5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
+        <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="19">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4827,40 +4877,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -4870,36 +4940,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>844.3</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>795.3</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>627.4</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>920.4</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="19">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="19">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="19">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="19">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="19">
         <f>J5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f>K5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f>L5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4909,40 +4999,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="19">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="19">
         <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -4952,40 +5062,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -4995,36 +5125,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>1069.3</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>1054.7</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>1183.4</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>1398.5</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="19">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="19">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="19">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="19">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="19">
         <f>J5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>K5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>L5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -5034,79 +5184,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>134.2</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>199.1</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>-13.9</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>-187.4</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="19">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="K13" s="19">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -5121,7 +5311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5321,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5178,6 +5373,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5185,24 +5405,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -5212,20 +5452,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -5234,24 +5489,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -5261,24 +5536,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="19">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -5288,8 +5583,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="12">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -5299,8 +5594,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!J11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -5310,7 +5605,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="18" t="n">
         <v>9874.6</v>
       </c>
     </row>
@@ -5320,8 +5615,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!J5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -5331,7 +5626,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5342,7 +5637,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -5353,7 +5648,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5364,8 +5659,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="12">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -5375,18 +5670,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -5397,7 +5692,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -5408,40 +5703,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5483,149 +5778,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.04854080987959798</v>
+      <c r="A5" s="15" t="n">
+        <v>0.06205716518069913</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.05604080987959798</v>
+      <c r="A6" s="15" t="n">
+        <v>0.06955716518069913</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.06354080987959798</v>
+      <c r="A7" s="15" t="n">
+        <v>0.07705716518069913</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.07104080987959799</v>
+      <c r="A8" s="15" t="n">
+        <v>0.08455716518069914</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.07854080987959798</v>
+      <c r="A9" s="15" t="n">
+        <v>0.09205716518069913</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -5661,7 +5956,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -5703,16 +5998,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-79.94526416405999</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-52.685458150872</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>18.165</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>339.016</v>
       </c>
     </row>
@@ -5722,17 +6017,17 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>3.84168e-07</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>3.84285e-07</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>3.5e-07</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>3.1e-07</v>
+      <c r="C6" s="25" t="n">
+        <v>3.84168e-13</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>3.84285e-13</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>3.5e-13</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>3.1e-13</v>
       </c>
     </row>
     <row r="7">
@@ -5741,16 +6036,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>2275.7</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>2205.6</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>2613.5</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>5242.1</v>
       </c>
     </row>
@@ -5760,16 +6055,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-208.1</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>-137.1</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>51.9</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>1093.6</v>
       </c>
     </row>
@@ -5779,16 +6074,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-208.1</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-137.1</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>51.9</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>1093.6</v>
       </c>
     </row>
@@ -5798,16 +6093,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>698</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>722.2</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>1245</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>3567.4</v>
       </c>
     </row>
@@ -5817,16 +6112,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>844.3</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>795.3</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>627.4</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>920.4</v>
       </c>
     </row>
@@ -5836,16 +6131,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>2718.1</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>2863.4</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>2991.4</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>3912.7</v>
       </c>
     </row>
@@ -5855,16 +6150,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>2067.6</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>2068.5</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>2665.4</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>6335.7</v>
       </c>
     </row>
@@ -5874,16 +6169,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>1223.3</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>1273.2</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>2038</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>5415.3</v>
       </c>
     </row>
@@ -5893,16 +6188,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-59.3</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>-38.3</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-21.8</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>-67.40000000000001</v>
       </c>
     </row>
@@ -5912,16 +6207,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>72.5</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>62.9</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>50.4</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>120.7</v>
       </c>
     </row>
@@ -5931,16 +6226,16 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>13.2</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>24.6</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>28.6</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>53.3</v>
       </c>
     </row>
@@ -5950,16 +6245,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>826.15473583594</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>806.614541849128</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>1211.265</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>2812.816</v>
       </c>
     </row>
@@ -5969,16 +6264,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>711</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>703.3</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>1245</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>3567.4</v>
       </c>
     </row>
@@ -5988,16 +6283,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>2850.3</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>3033.6</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>3108.4</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>4345.8</v>
       </c>
     </row>
@@ -6007,16 +6302,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>893.916246</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>895.037887</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>895.503589</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>897.339333</v>
       </c>
     </row>
@@ -6026,16 +6321,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>890.968721</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>893.318864</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>894.881526</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>894.972803</v>
       </c>
     </row>
@@ -6045,17 +6340,17 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
-        <v>7.8e-07</v>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>7.7e-07</v>
-      </c>
-      <c r="E23" s="29" t="n">
-        <v>1.38e-06</v>
-      </c>
-      <c r="F23" s="29" t="n">
-        <v>3.94e-06</v>
+      <c r="C23" s="25" t="n">
+        <v>7.8e-13</v>
+      </c>
+      <c r="D23" s="25" t="n">
+        <v>7.700000000000001e-13</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>1.38e-12</v>
+      </c>
+      <c r="F23" s="25" t="n">
+        <v>3.940000000000001e-12</v>
       </c>
     </row>
     <row r="24">
@@ -6064,17 +6359,17 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>8.000000000000001e-07</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>7.900000000000001e-07</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>1.39e-06</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>3.99e-06</v>
+      <c r="C24" s="25" t="n">
+        <v>8e-13</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>7.900000000000001e-13</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>1.39e-12</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>3.99e-12</v>
       </c>
     </row>
     <row r="25">
@@ -6083,16 +6378,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>701.3</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>692.2</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>1234.4</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>3538</v>
       </c>
     </row>
@@ -6102,16 +6397,16 @@
           <t>Average Dilution Earnings</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-11.1</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>-10.6</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-29.4</v>
       </c>
     </row>
@@ -6121,16 +6416,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>711</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>703.3</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>1245</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>3567.4</v>
       </c>
     </row>
@@ -6140,16 +6435,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>711</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>703.3</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>1245</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>3567.4</v>
       </c>
     </row>
@@ -6159,16 +6454,16 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>-10.7</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-23</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>-45.5</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-78</v>
       </c>
     </row>
@@ -6178,16 +6473,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>721.7</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>726.3</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>1290.5</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>3645.4</v>
       </c>
     </row>
@@ -6197,16 +6492,16 @@
           <t>Net Income Discontinuous Operations</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>-18.9</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6216,16 +6511,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>708.7</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>745.2</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>1290.5</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>3645.4</v>
       </c>
     </row>
@@ -6235,16 +6530,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>442.1</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>465.1</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>697.1</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>1649.2</v>
       </c>
     </row>
@@ -6254,16 +6549,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>1150.8</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>1210.3</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>1987.6</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>5294.6</v>
       </c>
     </row>
@@ -6273,16 +6568,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-226.3</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-218.5</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-83.8</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>956.5</v>
       </c>
     </row>
@@ -6292,16 +6587,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-15.3</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-48.8</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-82.09999999999999</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-134.8</v>
       </c>
     </row>
@@ -6311,16 +6606,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>-238.9</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>-131.8</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>58.4</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>1028.9</v>
       </c>
     </row>
@@ -6330,16 +6625,16 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>10.4</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>32.4</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>68.5</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -6349,7 +6644,7 @@
           <t>Gain On Sale Of Business</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6359,10 +6654,10 @@
           <t>Other Special Charges</t>
         </is>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>42.3</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>-720.5</v>
       </c>
     </row>
@@ -6372,16 +6667,16 @@
           <t>Write Off</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>113.6</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>-808.2</v>
       </c>
     </row>
@@ -6391,16 +6686,16 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>391.4</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>156.4</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>-281.3</v>
       </c>
     </row>
@@ -6410,16 +6705,16 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-255.7</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>7.8</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>6.6</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>61.7</v>
       </c>
     </row>
@@ -6429,16 +6724,16 @@
           <t>Earnings From Equity Interest</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>-2.9</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>-32.6</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>-53.6</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>-2.3</v>
       </c>
     </row>
@@ -6448,16 +6743,16 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>30.8</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>-5.3</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>-6.5</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>64.7</v>
       </c>
     </row>
@@ -6467,16 +6762,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>-59.3</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>-38.3</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>-21.8</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>-67.40000000000001</v>
       </c>
     </row>
@@ -6486,16 +6781,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>72.5</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>62.9</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>50.4</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>120.7</v>
       </c>
     </row>
@@ -6505,16 +6800,16 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>13.2</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>24.6</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>28.6</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>53.3</v>
       </c>
     </row>
@@ -6524,16 +6819,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1436.4</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>1467.1</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>2093.2</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>4405.5</v>
       </c>
     </row>
@@ -6543,16 +6838,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>132.2</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>170.2</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>117</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>433.1</v>
       </c>
     </row>
@@ -6562,16 +6857,16 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>78.8</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>298.5</v>
       </c>
     </row>
@@ -6581,16 +6876,16 @@
           <t>Provision For Doubtful Accounts</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>17.5</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>33.2</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6600,16 +6895,16 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>35.9</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>18.9</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>68.59999999999999</v>
       </c>
     </row>
@@ -6619,16 +6914,16 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>35.9</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>18.9</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>68.59999999999999</v>
       </c>
     </row>
@@ -6638,16 +6933,16 @@
           <t>Salaries And Wages</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>35.9</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>18.9</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>68.59999999999999</v>
       </c>
     </row>
@@ -6657,16 +6952,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>1568.6</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>1637.3</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>2210.2</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>4838.6</v>
       </c>
     </row>
@@ -6676,16 +6971,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>2718.1</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>2863.4</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>2991.4</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>3912.7</v>
       </c>
     </row>
@@ -6695,16 +6990,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>4286.7</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>4500.7</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>5201.6</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>8751.299999999999</v>
       </c>
     </row>
@@ -6714,16 +7009,16 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>4286.7</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>4500.7</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>5201.6</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>8751.299999999999</v>
       </c>
     </row>

--- a/docs/reports/GFI.xlsx
+++ b/docs/reports/GFI.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>58.37797951135433</v>
+        <v>59.87599642961217</v>
       </c>
     </row>
     <row r="8">
@@ -3374,13 +3374,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>87.03737370184209</v>
+        <v>92.46669730585675</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>79.37844742798252</v>
+        <v>84.46722651969691</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>95.62429432191867</v>
+        <v>101.4240529124515</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.3</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>58.37797951135433</v>
+        <v>59.87599642961217</v>
       </c>
     </row>
     <row r="21">
@@ -3592,7 +3592,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Target anchored 15% to the Street consensus ($54.28); model-only target $59.10.</t>
+          <t>Target anchored 15% to the Street consensus ($54.28); model-only target $60.86.</t>
         </is>
       </c>
     </row>
@@ -3704,31 +3704,31 @@
         <v>10939.125</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>11643.91000521689</v>
+        <v>11808.49458029313</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>12264.11978195723</v>
+        <v>12630.19823028071</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>12819.22049619522</v>
+        <v>13392.82877846781</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>13325.904900273</v>
+        <v>14088.12596299961</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>13797.81273554226</v>
+        <v>14711.65598247311</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>14245.75387532036</v>
+        <v>15263.47925043856</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>14678.12947531077</v>
+        <v>15748.99795456791</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>15101.38970019858</v>
+        <v>16180.63715776717</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>15478.92444270354</v>
+        <v>16585.15308671135</v>
       </c>
     </row>
     <row r="6">
@@ -3873,31 +3873,31 @@
         <v>5017.688009400001</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>5135.188063735764</v>
+        <v>5208.881971354399</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>5190.827561751298</v>
+        <v>5348.113271470289</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>5197.211834653883</v>
+        <v>5433.27659317539</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>5164.445171959616</v>
+        <v>5464.330918612266</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>5100.276968301623</v>
+        <v>5443.269682263205</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>5010.457836369158</v>
+        <v>5374.012883765426</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>4899.138625001247</v>
+        <v>5262.287630092867</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>5042.673085619126</v>
+        <v>5408.663539213931</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>5170.701287759604</v>
+        <v>5545.841502694278</v>
       </c>
     </row>
     <row r="10">
@@ -3957,31 +3957,31 @@
         <v>4354.242269607347</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>4438.499337886294</v>
+        <v>4507.960395042147</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>4524.715468845498</v>
+        <v>4668.76251164849</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>4572.950611125078</v>
+        <v>4787.716168004848</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>4591.318735028943</v>
+        <v>4864.219135453242</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>4586.078981079316</v>
+        <v>4899.386662444587</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>4561.91298090575</v>
+        <v>4896.033880127997</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>4522.236594737328</v>
+        <v>4858.672346102398</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>4742.923531640906</v>
+        <v>5086.697699721502</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>4952.438079472667</v>
+        <v>5311.979729156002</v>
       </c>
     </row>
     <row r="13">
@@ -4315,28 +4315,28 @@
         <v>0.25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.06442791404402876</v>
+        <v>0.07947341129140811</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.05326473465206037</v>
+        <v>0.06958580913090329</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.04526217324252213</v>
+        <v>0.06038151850686814</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.03952536772638876</v>
+        <v>0.05191563306249747</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.03541281727589028</v>
+        <v>0.04425925925925926</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.032464648445636</v>
+        <v>0.0375092558324419</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.03035119122333507</v>
+        <v>0.03180917641142601</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.02883611468339666</v>
+        <v>0.02740740740740741</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
